--- a/vse-loti/340815310/spec-340815310.xlsx
+++ b/vse-loti/340815310/spec-340815310.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:I235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -558,7 +561,7 @@
         <v>116393.44</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +596,7 @@
         <v>145081.97</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>174098.36</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +631,7 @@
         <v>128688.52</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +666,7 @@
         <v>116393.44</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="6">
@@ -698,7 +701,7 @@
         <v>118852.46</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +736,7 @@
         <v>219672.13</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>263606.56</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -768,7 +771,7 @@
         <v>232786.89</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="9">
@@ -803,7 +806,7 @@
         <v>157377.05</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +841,7 @@
         <v>204180.33</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>245016.39</v>
+        <v>249100</v>
       </c>
     </row>
     <row r="11">
@@ -873,7 +876,7 @@
         <v>251065.57</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>301278.69</v>
+        <v>306300</v>
       </c>
     </row>
     <row r="12">
@@ -908,7 +911,7 @@
         <v>274590.16</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="13">
@@ -943,7 +946,7 @@
         <v>116393.44</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="14">
@@ -978,7 +981,7 @@
         <v>128688.52</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="15">
@@ -1013,7 +1016,7 @@
         <v>116393.44</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="16">
@@ -1048,7 +1051,7 @@
         <v>128688.52</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="17">
@@ -1083,7 +1086,7 @@
         <v>204180.33</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>245016.39</v>
+        <v>249100</v>
       </c>
     </row>
     <row r="18">
@@ -1118,7 +1121,7 @@
         <v>116393.44</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="19">
@@ -1153,7 +1156,7 @@
         <v>116393.44</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="20">
@@ -1188,7 +1191,7 @@
         <v>116393.44</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="21">
@@ -1223,7 +1226,7 @@
         <v>227622.95</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>273147.54</v>
+        <v>277700</v>
       </c>
     </row>
     <row r="22">
@@ -1258,7 +1261,7 @@
         <v>210655.74</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>252786.89</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="23">
@@ -1293,7 +1296,7 @@
         <v>225409.84</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>270491.8</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="24">
@@ -1328,7 +1331,7 @@
         <v>225409.84</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>270491.8</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="25">
@@ -1363,7 +1366,7 @@
         <v>116393.44</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="26">
@@ -1398,7 +1401,7 @@
         <v>149180.33</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>179016.39</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="27">
@@ -1433,7 +1436,7 @@
         <v>128688.52</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="28">
@@ -1468,7 +1471,7 @@
         <v>143442.62</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>172131.15</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="29">
@@ -1503,7 +1506,7 @@
         <v>116393.44</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="30">
@@ -1538,7 +1541,7 @@
         <v>128688.52</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="31">
@@ -1573,7 +1576,7 @@
         <v>116393.44</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="32">
@@ -1608,7 +1611,7 @@
         <v>128688.52</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="33">
@@ -1643,7 +1646,7 @@
         <v>116393.44</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="34">
@@ -1678,7 +1681,7 @@
         <v>116393.44</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="35">
@@ -1713,7 +1716,7 @@
         <v>116393.44</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="36">
@@ -1748,7 +1751,7 @@
         <v>293196.72</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>351836.07</v>
+        <v>357700</v>
       </c>
     </row>
     <row r="37">
@@ -1783,7 +1786,7 @@
         <v>118852.46</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="38">
@@ -1818,7 +1821,7 @@
         <v>274590.16</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="39">
@@ -1853,7 +1856,7 @@
         <v>128688.52</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="40">
@@ -1888,7 +1891,7 @@
         <v>116393.44</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="41">
@@ -1923,7 +1926,7 @@
         <v>116393.44</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="42">
@@ -1958,7 +1961,7 @@
         <v>116393.44</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="43">
@@ -1993,7 +1996,7 @@
         <v>116393.44</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="44">
@@ -2028,7 +2031,7 @@
         <v>116393.44</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="45">
@@ -2063,7 +2066,7 @@
         <v>116393.44</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="46">
@@ -2098,7 +2101,7 @@
         <v>116393.44</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="47">
@@ -2133,7 +2136,7 @@
         <v>118852.46</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="48">
@@ -2168,7 +2171,7 @@
         <v>116393.44</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="49">
@@ -2203,7 +2206,7 @@
         <v>120491.8</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="50">
@@ -2238,7 +2241,7 @@
         <v>116393.44</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="51">
@@ -2273,7 +2276,7 @@
         <v>128688.52</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="52">
@@ -2308,7 +2311,7 @@
         <v>116393.44</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="53">
@@ -2343,7 +2346,7 @@
         <v>161475.41</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>193770.49</v>
+        <v>197000</v>
       </c>
     </row>
     <row r="54">
@@ -2378,7 +2381,7 @@
         <v>116393.44</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="55">
@@ -2413,7 +2416,7 @@
         <v>116393.44</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="56">
@@ -2448,7 +2451,7 @@
         <v>118852.46</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="57">
@@ -2483,7 +2486,7 @@
         <v>128688.52</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="58">
@@ -2518,7 +2521,7 @@
         <v>116393.44</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="59">
@@ -2553,7 +2556,7 @@
         <v>232786.89</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="60">
@@ -2588,7 +2591,7 @@
         <v>116393.44</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="61">
@@ -2623,7 +2626,7 @@
         <v>206557.38</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>247868.85</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="62">
@@ -2658,7 +2661,7 @@
         <v>116393.44</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="63">
@@ -2693,7 +2696,7 @@
         <v>128688.52</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="64">
@@ -2728,7 +2731,7 @@
         <v>206557.38</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>247868.85</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="65">
@@ -2763,7 +2766,7 @@
         <v>157377.05</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="66">
@@ -2798,7 +2801,7 @@
         <v>225409.84</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>270491.8</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="67">
@@ -2833,7 +2836,7 @@
         <v>143442.62</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>172131.15</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="68">
@@ -2868,7 +2871,7 @@
         <v>116393.44</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="69">
@@ -2903,7 +2906,7 @@
         <v>120491.8</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="70">
@@ -2938,7 +2941,7 @@
         <v>157377.05</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="71">
@@ -2973,7 +2976,7 @@
         <v>157377.05</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="72">
@@ -3008,7 +3011,7 @@
         <v>116393.44</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="73">
@@ -3043,7 +3046,7 @@
         <v>116393.44</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="74">
@@ -3078,7 +3081,7 @@
         <v>116393.44</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="75">
@@ -3113,7 +3116,7 @@
         <v>116393.44</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="76">
@@ -3148,7 +3151,7 @@
         <v>116393.44</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="77">
@@ -3183,7 +3186,7 @@
         <v>116393.44</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="78">
@@ -3218,7 +3221,7 @@
         <v>251065.57</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>301278.69</v>
+        <v>306300</v>
       </c>
     </row>
     <row r="79">
@@ -3253,7 +3256,7 @@
         <v>224590.16</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>269508.2</v>
+        <v>274000</v>
       </c>
     </row>
     <row r="80">
@@ -3288,7 +3291,7 @@
         <v>206557.38</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>247868.85</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="81">
@@ -3323,7 +3326,7 @@
         <v>128688.52</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="82">
@@ -3358,7 +3361,7 @@
         <v>116393.44</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="83">
@@ -3393,7 +3396,7 @@
         <v>116393.44</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="84">
@@ -3428,7 +3431,7 @@
         <v>157377.05</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="85">
@@ -3463,7 +3466,7 @@
         <v>116393.44</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="86">
@@ -3498,7 +3501,7 @@
         <v>116393.44</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="87">
@@ -3533,7 +3536,7 @@
         <v>116393.44</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="88">
@@ -3568,7 +3571,7 @@
         <v>116393.44</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="89">
@@ -3603,7 +3606,7 @@
         <v>116393.44</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="90">
@@ -3638,7 +3641,7 @@
         <v>116393.44</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="91">
@@ -3673,7 +3676,7 @@
         <v>275655.74</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>330786.89</v>
+        <v>336300</v>
       </c>
     </row>
     <row r="92">
@@ -3708,7 +3711,7 @@
         <v>128688.52</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="93">
@@ -3743,7 +3746,7 @@
         <v>145081.97</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>174098.36</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="94">
@@ -3778,7 +3781,7 @@
         <v>145081.97</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>174098.36</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="95">
@@ -3813,7 +3816,7 @@
         <v>116393.44</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="96">
@@ -3848,7 +3851,7 @@
         <v>275655.74</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>330786.89</v>
+        <v>336300</v>
       </c>
     </row>
     <row r="97">
@@ -3883,7 +3886,7 @@
         <v>116393.44</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="98">
@@ -3918,7 +3921,7 @@
         <v>116393.44</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="99">
@@ -3953,7 +3956,7 @@
         <v>145081.97</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>174098.36</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="100">
@@ -3988,7 +3991,7 @@
         <v>116393.44</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="101">
@@ -4023,7 +4026,7 @@
         <v>145081.97</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>174098.36</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="102">
@@ -4058,7 +4061,7 @@
         <v>128688.52</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="103">
@@ -4093,7 +4096,7 @@
         <v>128688.52</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="104">
@@ -4128,7 +4131,7 @@
         <v>128688.52</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="105">
@@ -4163,7 +4166,7 @@
         <v>265000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>318000</v>
+        <v>323300</v>
       </c>
     </row>
     <row r="106">
@@ -4198,7 +4201,7 @@
         <v>192622.95</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>231147.54</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="107">
@@ -4233,7 +4236,7 @@
         <v>203524.59</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="108">
@@ -4268,7 +4271,7 @@
         <v>118852.46</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="109">
@@ -4303,7 +4306,7 @@
         <v>203524.59</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="110">
@@ -4338,7 +4341,7 @@
         <v>118852.46</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="111">
@@ -4373,7 +4376,7 @@
         <v>203524.59</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="112">
@@ -4408,7 +4411,7 @@
         <v>118852.46</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="113">
@@ -4443,7 +4446,7 @@
         <v>203524.59</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="114">
@@ -4478,7 +4481,7 @@
         <v>118852.46</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="115">
@@ -4513,7 +4516,7 @@
         <v>118852.46</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="116">
@@ -4548,7 +4551,7 @@
         <v>274590.16</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="117">
@@ -4583,7 +4586,7 @@
         <v>118852.46</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="118">
@@ -4618,7 +4621,7 @@
         <v>118852.46</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="119">
@@ -4653,7 +4656,7 @@
         <v>118852.46</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="120">
@@ -4688,7 +4691,7 @@
         <v>118852.46</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="121">
@@ -4723,7 +4726,7 @@
         <v>274590.16</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="122">
@@ -4758,7 +4761,7 @@
         <v>118852.46</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="123">
@@ -4793,7 +4796,7 @@
         <v>274590.16</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="124">
@@ -4828,7 +4831,7 @@
         <v>116393.44</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="125">
@@ -4863,7 +4866,7 @@
         <v>118852.46</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="126">
@@ -4898,7 +4901,7 @@
         <v>120491.8</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="127">
@@ -4933,7 +4936,7 @@
         <v>143442.62</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>172131.15</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="128">
@@ -4968,7 +4971,7 @@
         <v>274590.16</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>329508.2</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="129">
@@ -5003,7 +5006,7 @@
         <v>118852.46</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="130">
@@ -5038,7 +5041,7 @@
         <v>116393.44</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="131">
@@ -5073,7 +5076,7 @@
         <v>120491.8</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="132">
@@ -5108,7 +5111,7 @@
         <v>203524.59</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="133">
@@ -5143,7 +5146,7 @@
         <v>161475.41</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>193770.49</v>
+        <v>197000</v>
       </c>
     </row>
     <row r="134">
@@ -5178,7 +5181,7 @@
         <v>192622.95</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>231147.54</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="135">
@@ -5213,7 +5216,7 @@
         <v>118852.46</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="136">
@@ -5248,7 +5251,7 @@
         <v>118852.46</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="137">
@@ -5283,7 +5286,7 @@
         <v>128688.52</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="138">
@@ -5318,7 +5321,7 @@
         <v>116393.44</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="139">
@@ -5353,7 +5356,7 @@
         <v>232786.89</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="140">
@@ -5388,7 +5391,7 @@
         <v>251065.57</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>301278.69</v>
+        <v>306300</v>
       </c>
     </row>
     <row r="141">
@@ -5423,7 +5426,7 @@
         <v>219672.13</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>263606.56</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="142">
@@ -5458,7 +5461,7 @@
         <v>116393.44</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="143">
@@ -5493,7 +5496,7 @@
         <v>120491.8</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="144">
@@ -5528,7 +5531,7 @@
         <v>118852.46</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="145">
@@ -5563,7 +5566,7 @@
         <v>143442.62</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>172131.15</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="146">
@@ -5598,7 +5601,7 @@
         <v>116393.44</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="147">
@@ -5633,7 +5636,7 @@
         <v>116393.44</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="148">
@@ -5668,7 +5671,7 @@
         <v>116393.44</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="149">
@@ -5703,7 +5706,7 @@
         <v>116393.44</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="150">
@@ -5738,7 +5741,7 @@
         <v>157377.05</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="151">
@@ -5773,7 +5776,7 @@
         <v>128688.52</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="152">
@@ -5808,7 +5811,7 @@
         <v>116393.44</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="153">
@@ -5843,7 +5846,7 @@
         <v>128688.52</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="154">
@@ -5878,7 +5881,7 @@
         <v>116393.44</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="155">
@@ -5913,7 +5916,7 @@
         <v>118852.46</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="156">
@@ -5948,7 +5951,7 @@
         <v>116393.44</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="157">
@@ -5983,7 +5986,7 @@
         <v>116393.44</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="158">
@@ -6018,7 +6021,7 @@
         <v>116393.44</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="159">
@@ -6053,7 +6056,7 @@
         <v>116393.44</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="160">
@@ -6088,7 +6091,7 @@
         <v>293196.72</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>351836.07</v>
+        <v>357700</v>
       </c>
     </row>
     <row r="161">
@@ -6123,7 +6126,7 @@
         <v>219672.13</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>263606.56</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="162">
@@ -6158,7 +6161,7 @@
         <v>128688.52</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="163">
@@ -6193,7 +6196,7 @@
         <v>128688.52</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="164">
@@ -6228,7 +6231,7 @@
         <v>128688.52</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="165">
@@ -6263,7 +6266,7 @@
         <v>128688.52</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="166">
@@ -6298,7 +6301,7 @@
         <v>118852.46</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="167">
@@ -6333,7 +6336,7 @@
         <v>118852.46</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="168">
@@ -6368,7 +6371,7 @@
         <v>116393.44</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="169">
@@ -6403,7 +6406,7 @@
         <v>116393.44</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="170">
@@ -6438,7 +6441,7 @@
         <v>116393.44</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="171">
@@ -6473,7 +6476,7 @@
         <v>116393.44</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="172">
@@ -6508,7 +6511,7 @@
         <v>116393.44</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="173">
@@ -6543,7 +6546,7 @@
         <v>116393.44</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="174">
@@ -6578,7 +6581,7 @@
         <v>116393.44</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="175">
@@ -6613,7 +6616,7 @@
         <v>116393.44</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="176">
@@ -6648,7 +6651,7 @@
         <v>116393.44</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="177">
@@ -6683,7 +6686,7 @@
         <v>116393.44</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="178">
@@ -6718,7 +6721,7 @@
         <v>116393.44</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="179">
@@ -6753,7 +6756,7 @@
         <v>116393.44</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="180">
@@ -6788,7 +6791,7 @@
         <v>116393.44</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="181">
@@ -6823,7 +6826,7 @@
         <v>116393.44</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="182">
@@ -6858,7 +6861,7 @@
         <v>116393.44</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="183">
@@ -6893,7 +6896,7 @@
         <v>116393.44</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="184">
@@ -6928,7 +6931,7 @@
         <v>232786.89</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="185">
@@ -6963,7 +6966,7 @@
         <v>232786.89</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="186">
@@ -6998,7 +7001,7 @@
         <v>232786.89</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="187">
@@ -7033,7 +7036,7 @@
         <v>70491.8</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>84590.16</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="188">
@@ -7068,7 +7071,7 @@
         <v>206557.38</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>247868.85</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="189">
@@ -7103,7 +7106,7 @@
         <v>232786.89</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="190">
@@ -7138,7 +7141,7 @@
         <v>118852.46</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="191">
@@ -7173,7 +7176,7 @@
         <v>192622.95</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>231147.54</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="192">
@@ -7208,7 +7211,7 @@
         <v>206557.38</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>247868.85</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="193">
@@ -7243,7 +7246,7 @@
         <v>232786.89</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="194">
@@ -7278,7 +7281,7 @@
         <v>118852.46</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="195">
@@ -7313,7 +7316,7 @@
         <v>116393.44</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="196">
@@ -7348,7 +7351,7 @@
         <v>116393.44</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="197">
@@ -7383,7 +7386,7 @@
         <v>116393.44</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="198">
@@ -7418,7 +7421,7 @@
         <v>116393.44</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="199">
@@ -7453,7 +7456,7 @@
         <v>116393.44</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="200">
@@ -7488,7 +7491,7 @@
         <v>232786.89</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="201">
@@ -7523,7 +7526,7 @@
         <v>116393.44</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="202">
@@ -7558,7 +7561,7 @@
         <v>116393.44</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="203">
@@ -7593,7 +7596,7 @@
         <v>203524.59</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>244229.51</v>
+        <v>248300</v>
       </c>
     </row>
     <row r="204">
@@ -7628,7 +7631,7 @@
         <v>116393.44</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="205">
@@ -7663,7 +7666,7 @@
         <v>118852.46</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>142622.95</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="206">
@@ -7698,7 +7701,7 @@
         <v>116393.44</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="207">
@@ -7733,7 +7736,7 @@
         <v>116393.44</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="208">
@@ -7768,7 +7771,7 @@
         <v>116393.44</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="209">
@@ -7803,7 +7806,7 @@
         <v>116393.44</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="210">
@@ -7838,7 +7841,7 @@
         <v>116393.44</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="211">
@@ -7873,7 +7876,7 @@
         <v>116393.44</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="212">
@@ -7908,7 +7911,7 @@
         <v>363442.62</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>436131.15</v>
+        <v>443400</v>
       </c>
     </row>
     <row r="213">
@@ -7943,7 +7946,7 @@
         <v>265000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>318000</v>
+        <v>323300</v>
       </c>
     </row>
     <row r="214">
@@ -7978,7 +7981,7 @@
         <v>143442.62</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>172131.15</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="215">
@@ -8013,7 +8016,7 @@
         <v>210655.74</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>252786.89</v>
+        <v>257000</v>
       </c>
     </row>
     <row r="216">
@@ -8048,7 +8051,7 @@
         <v>120491.8</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>144590.16</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="217">
@@ -8083,7 +8086,7 @@
         <v>232786.89</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>279344.26</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="218">
@@ -8118,7 +8121,7 @@
         <v>149180.33</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>179016.39</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="219">
@@ -8153,7 +8156,7 @@
         <v>116393.44</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="220">
@@ -8188,7 +8191,7 @@
         <v>128688.52</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="221">
@@ -8223,7 +8226,7 @@
         <v>116393.44</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="222">
@@ -8258,7 +8261,7 @@
         <v>116393.44</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="223">
@@ -8293,7 +8296,7 @@
         <v>116393.44</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="224">
@@ -8328,7 +8331,7 @@
         <v>128688.52</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>154426.23</v>
+        <v>157000</v>
       </c>
     </row>
     <row r="225">
@@ -8363,7 +8366,7 @@
         <v>116393.44</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>139672.13</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="226">
@@ -8398,7 +8401,7 @@
         <v>200819.67</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>240983.61</v>
+        <v>245000</v>
       </c>
     </row>
     <row r="227">
@@ -8433,7 +8436,7 @@
         <v>157377.05</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>188852.46</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="228">
@@ -8459,19 +8462,36 @@
         <v>9549463.44262295</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="n">
+        <v>11650345.4</v>
+      </c>
+    </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
+          <t>НДС 22 %, ставка из документа: "Начальная (максимальная) цена с НДС 22% руб." — Приложение №4. Сведения о НМЦ.txt; суммы источника указаны без НДС: "без НДС" — ТЗ БС Ремонт.txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
           <t>Источник: СПЕЦИФИКАЦИЯ прил  1.xlsx
 ТЗ БС Ремонт.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="232"/>
-    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A231:B233"/>
+    <mergeCell ref="A233:B235"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340815310/spec-340815310.xlsx
+++ b/vse-loti/340815310/spec-340815310.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I235"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -555,13 +561,16 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I2" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +599,16 @@
         <v>0.2</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>145081.97</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>29016.39</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>145081.97</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>177000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>35400</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +637,16 @@
         <v>0.2</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>25737.7</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>31399.99</v>
       </c>
     </row>
     <row r="5">
@@ -660,13 +675,16 @@
         <v>0.5</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I5" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +713,16 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>59426.23</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>72500</v>
       </c>
     </row>
     <row r="7">
@@ -730,13 +751,16 @@
         <v>0.1</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>219672.13</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>21967.21</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>219672.13</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>268000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>26800</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +789,16 @@
         <v>0.2</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>46557.38</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="9">
@@ -800,13 +827,16 @@
         <v>1.1</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>173114.75</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>211199.99</v>
       </c>
     </row>
     <row r="10">
@@ -835,13 +865,16 @@
         <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>204180.33</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>4083.61</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>204180.33</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>249100</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4982</v>
       </c>
     </row>
     <row r="11">
@@ -870,13 +903,16 @@
         <v>0.02</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>251065.57</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>5021.31</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>251065.57</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>306300</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>6126</v>
       </c>
     </row>
     <row r="12">
@@ -905,13 +941,16 @@
         <v>0.016</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>4393.44</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5360</v>
       </c>
     </row>
     <row r="13">
@@ -940,13 +979,16 @@
         <v>0.237</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>27585.25</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I13" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>33654</v>
       </c>
     </row>
     <row r="14">
@@ -975,13 +1017,16 @@
         <v>0.04</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>5147.54</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>6280</v>
       </c>
     </row>
     <row r="15">
@@ -1010,13 +1055,16 @@
         <v>1.811</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>210788.52</v>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I15" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>257161.99</v>
       </c>
     </row>
     <row r="16">
@@ -1045,13 +1093,16 @@
         <v>0.09</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>11581.97</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>14130</v>
       </c>
     </row>
     <row r="17">
@@ -1080,13 +1131,16 @@
         <v>0.02</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>204180.33</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>4083.61</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>204180.33</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>249100</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>4982</v>
       </c>
     </row>
     <row r="18">
@@ -1115,13 +1169,16 @@
         <v>2.5</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>290983.61</v>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I18" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>355000</v>
       </c>
     </row>
     <row r="19">
@@ -1150,13 +1207,16 @@
         <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>232786.89</v>
       </c>
-      <c r="H19" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I19" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>284000.01</v>
       </c>
     </row>
     <row r="20">
@@ -1185,13 +1245,16 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>174590.16</v>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I20" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>213000</v>
       </c>
     </row>
     <row r="21">
@@ -1220,13 +1283,16 @@
         <v>0.1</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>227622.95</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>22762.3</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>227622.95</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>277700</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>27770.01</v>
       </c>
     </row>
     <row r="22">
@@ -1255,13 +1321,16 @@
         <v>0.1</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>210655.74</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>21065.57</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>210655.74</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>257000</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>25700</v>
       </c>
     </row>
     <row r="23">
@@ -1290,13 +1359,16 @@
         <v>0.1</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>225409.84</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>22540.98</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>225409.84</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>275000</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>27500</v>
       </c>
     </row>
     <row r="24">
@@ -1325,13 +1397,16 @@
         <v>0.1</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>225409.84</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>22540.98</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>225409.84</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>275000</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>27500</v>
       </c>
     </row>
     <row r="25">
@@ -1360,13 +1435,16 @@
         <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>232786.89</v>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I25" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>284000.01</v>
       </c>
     </row>
     <row r="26">
@@ -1395,13 +1473,16 @@
         <v>0.277</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>149180.33</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>41322.95</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>149180.33</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>182000</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>50414</v>
       </c>
     </row>
     <row r="27">
@@ -1430,13 +1511,16 @@
         <v>0.17</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>21877.05</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>26690</v>
       </c>
     </row>
     <row r="28">
@@ -1465,13 +1549,16 @@
         <v>1.245</v>
       </c>
       <c r="G28" s="5" t="n">
+        <v>143442.62</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>178586.07</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>143442.62</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>175000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>217875.01</v>
       </c>
     </row>
     <row r="29">
@@ -1500,13 +1587,16 @@
         <v>0.75</v>
       </c>
       <c r="G29" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>87295.08</v>
       </c>
-      <c r="H29" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I29" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>106500</v>
       </c>
     </row>
     <row r="30">
@@ -1535,13 +1625,16 @@
         <v>0.25</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>32172.13</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>39250</v>
       </c>
     </row>
     <row r="31">
@@ -1570,13 +1663,16 @@
         <v>0.25</v>
       </c>
       <c r="G31" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>29098.36</v>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I31" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>35500</v>
       </c>
     </row>
     <row r="32">
@@ -1605,13 +1701,16 @@
         <v>0.4</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>51475.41</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>62800</v>
       </c>
     </row>
     <row r="33">
@@ -1640,13 +1739,16 @@
         <v>0.17</v>
       </c>
       <c r="G33" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>19786.89</v>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I33" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>24140.01</v>
       </c>
     </row>
     <row r="34">
@@ -1675,13 +1777,16 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I34" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="35">
@@ -1710,13 +1815,16 @@
         <v>0.85</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>98934.42999999999</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I35" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>120700</v>
       </c>
     </row>
     <row r="36">
@@ -1745,13 +1853,16 @@
         <v>0.04</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>293196.72</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>11727.87</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>293196.72</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>357700</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>14308</v>
       </c>
     </row>
     <row r="37">
@@ -1780,13 +1891,16 @@
         <v>0.417</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>49561.48</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>60465.01</v>
       </c>
     </row>
     <row r="38">
@@ -1815,13 +1929,16 @@
         <v>0.1</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>27459.02</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>33500</v>
       </c>
     </row>
     <row r="39">
@@ -1850,13 +1967,16 @@
         <v>0.6</v>
       </c>
       <c r="G39" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>77213.11</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>94199.99000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1885,13 +2005,16 @@
         <v>0.28</v>
       </c>
       <c r="G40" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>32590.16</v>
       </c>
-      <c r="H40" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I40" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>39760</v>
       </c>
     </row>
     <row r="41">
@@ -1920,13 +2043,16 @@
         <v>0.4</v>
       </c>
       <c r="G41" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H41" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I41" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="42">
@@ -1955,13 +2081,16 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H42" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I42" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="43">
@@ -1990,13 +2119,16 @@
         <v>0.85</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>98934.42999999999</v>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I43" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>120700</v>
       </c>
     </row>
     <row r="44">
@@ -2025,13 +2157,16 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I44" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="45">
@@ -2060,13 +2195,16 @@
         <v>0.55</v>
       </c>
       <c r="G45" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>64016.39</v>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I45" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>78100</v>
       </c>
     </row>
     <row r="46">
@@ -2095,13 +2233,16 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H46" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H46" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I46" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="47">
@@ -2130,13 +2271,16 @@
         <v>1.083</v>
       </c>
       <c r="G47" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>128717.21</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>157035</v>
       </c>
     </row>
     <row r="48">
@@ -2165,13 +2309,16 @@
         <v>0.4</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I48" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="49">
@@ -2200,13 +2347,16 @@
         <v>0.869</v>
       </c>
       <c r="G49" s="5" t="n">
+        <v>120491.8</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>104707.38</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>120491.8</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>147000</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>127743</v>
       </c>
     </row>
     <row r="50">
@@ -2235,13 +2385,16 @@
         <v>0.413</v>
       </c>
       <c r="G50" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <v>48070.49</v>
       </c>
-      <c r="H50" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I50" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>58646</v>
       </c>
     </row>
     <row r="51">
@@ -2270,13 +2423,16 @@
         <v>2</v>
       </c>
       <c r="G51" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>257377.05</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>314000</v>
       </c>
     </row>
     <row r="52">
@@ -2305,13 +2461,16 @@
         <v>1.5</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H52" s="5" t="n">
         <v>174590.16</v>
       </c>
-      <c r="H52" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I52" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>213000</v>
       </c>
     </row>
     <row r="53">
@@ -2340,13 +2499,16 @@
         <v>0.036</v>
       </c>
       <c r="G53" s="5" t="n">
+        <v>161475.41</v>
+      </c>
+      <c r="H53" s="5" t="n">
         <v>5813.11</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>161475.41</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>197000</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>7091.99</v>
       </c>
     </row>
     <row r="54">
@@ -2375,13 +2537,16 @@
         <v>0.6</v>
       </c>
       <c r="G54" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H54" s="5" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H54" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I54" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>85200.00999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2410,13 +2575,16 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H55" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I55" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="56">
@@ -2445,13 +2613,16 @@
         <v>0.65</v>
       </c>
       <c r="G56" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H56" s="5" t="n">
         <v>77254.10000000001</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>94250</v>
       </c>
     </row>
     <row r="57">
@@ -2480,13 +2651,16 @@
         <v>0.4</v>
       </c>
       <c r="G57" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H57" s="5" t="n">
         <v>51475.41</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>62800</v>
       </c>
     </row>
     <row r="58">
@@ -2515,13 +2689,16 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H58" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H58" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I58" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="59">
@@ -2550,13 +2727,16 @@
         <v>0.1</v>
       </c>
       <c r="G59" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H59" s="5" t="n">
         <v>23278.69</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="60">
@@ -2585,13 +2765,16 @@
         <v>0.2</v>
       </c>
       <c r="G60" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H60" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H60" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I60" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="61">
@@ -2620,13 +2803,16 @@
         <v>0.15</v>
       </c>
       <c r="G61" s="5" t="n">
+        <v>206557.38</v>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>30983.61</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>206557.38</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>252000</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>37800</v>
       </c>
     </row>
     <row r="62">
@@ -2655,13 +2841,16 @@
         <v>0.4</v>
       </c>
       <c r="G62" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H62" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H62" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I62" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="63">
@@ -2690,13 +2879,16 @@
         <v>0.3</v>
       </c>
       <c r="G63" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>38606.56</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>47100</v>
       </c>
     </row>
     <row r="64">
@@ -2725,13 +2917,16 @@
         <v>0.2</v>
       </c>
       <c r="G64" s="5" t="n">
+        <v>206557.38</v>
+      </c>
+      <c r="H64" s="5" t="n">
         <v>41311.48</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>206557.38</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>252000</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>50400.01</v>
       </c>
     </row>
     <row r="65">
@@ -2760,13 +2955,16 @@
         <v>0.3</v>
       </c>
       <c r="G65" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H65" s="5" t="n">
         <v>47213.11</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>57599.99</v>
       </c>
     </row>
     <row r="66">
@@ -2795,13 +2993,16 @@
         <v>0.2</v>
       </c>
       <c r="G66" s="5" t="n">
+        <v>225409.84</v>
+      </c>
+      <c r="H66" s="5" t="n">
         <v>45081.97</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>225409.84</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>275000</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>55000</v>
       </c>
     </row>
     <row r="67">
@@ -2830,13 +3031,16 @@
         <v>0.8</v>
       </c>
       <c r="G67" s="5" t="n">
+        <v>143442.62</v>
+      </c>
+      <c r="H67" s="5" t="n">
         <v>114754.1</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>143442.62</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>175000</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>140000</v>
       </c>
     </row>
     <row r="68">
@@ -2865,13 +3069,16 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H68" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I68" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="69">
@@ -2900,13 +3107,16 @@
         <v>0.6</v>
       </c>
       <c r="G69" s="5" t="n">
+        <v>120491.8</v>
+      </c>
+      <c r="H69" s="5" t="n">
         <v>72295.08</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>120491.8</v>
       </c>
       <c r="I69" s="5" t="n">
         <v>147000</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>88200</v>
       </c>
     </row>
     <row r="70">
@@ -2935,13 +3145,16 @@
         <v>0.8</v>
       </c>
       <c r="G70" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H70" s="5" t="n">
         <v>125901.64</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>153600</v>
       </c>
     </row>
     <row r="71">
@@ -2970,13 +3183,16 @@
         <v>0.8</v>
       </c>
       <c r="G71" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H71" s="5" t="n">
         <v>125901.64</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>153600</v>
       </c>
     </row>
     <row r="72">
@@ -3005,13 +3221,16 @@
         <v>0.3</v>
       </c>
       <c r="G72" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H72" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I72" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="73">
@@ -3040,13 +3259,16 @@
         <v>0.3</v>
       </c>
       <c r="G73" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H73" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H73" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I73" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="74">
@@ -3075,13 +3297,16 @@
         <v>0.3</v>
       </c>
       <c r="G74" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H74" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H74" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I74" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="75">
@@ -3110,13 +3335,16 @@
         <v>0.4</v>
       </c>
       <c r="G75" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H75" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I75" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="76">
@@ -3145,13 +3373,16 @@
         <v>0.6</v>
       </c>
       <c r="G76" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H76" s="5" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H76" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I76" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>85200.00999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3180,13 +3411,16 @@
         <v>0.3</v>
       </c>
       <c r="G77" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H77" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H77" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I77" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="78">
@@ -3215,13 +3449,16 @@
         <v>0.01</v>
       </c>
       <c r="G78" s="5" t="n">
+        <v>251065.57</v>
+      </c>
+      <c r="H78" s="5" t="n">
         <v>2510.66</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>251065.57</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>306300</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>3063.01</v>
       </c>
     </row>
     <row r="79">
@@ -3250,13 +3487,16 @@
         <v>0.015</v>
       </c>
       <c r="G79" s="5" t="n">
+        <v>224590.16</v>
+      </c>
+      <c r="H79" s="5" t="n">
         <v>3368.85</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>224590.16</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>274000</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>4110</v>
       </c>
     </row>
     <row r="80">
@@ -3285,13 +3525,16 @@
         <v>0.1</v>
       </c>
       <c r="G80" s="5" t="n">
+        <v>206557.38</v>
+      </c>
+      <c r="H80" s="5" t="n">
         <v>20655.74</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>206557.38</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>252000</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="81">
@@ -3320,13 +3563,16 @@
         <v>0.16</v>
       </c>
       <c r="G81" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H81" s="5" t="n">
         <v>20590.16</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>25120</v>
       </c>
     </row>
     <row r="82">
@@ -3355,13 +3601,16 @@
         <v>0.45</v>
       </c>
       <c r="G82" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H82" s="5" t="n">
         <v>52377.05</v>
       </c>
-      <c r="H82" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I82" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>63900</v>
       </c>
     </row>
     <row r="83">
@@ -3390,13 +3639,16 @@
         <v>0.45</v>
       </c>
       <c r="G83" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H83" s="5" t="n">
         <v>52377.05</v>
       </c>
-      <c r="H83" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I83" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>63900</v>
       </c>
     </row>
     <row r="84">
@@ -3425,13 +3677,16 @@
         <v>0.4</v>
       </c>
       <c r="G84" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H84" s="5" t="n">
         <v>62950.82</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I84" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>76800</v>
       </c>
     </row>
     <row r="85">
@@ -3460,13 +3715,16 @@
         <v>0.4</v>
       </c>
       <c r="G85" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H85" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H85" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I85" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="86">
@@ -3495,13 +3753,16 @@
         <v>0.25</v>
       </c>
       <c r="G86" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H86" s="5" t="n">
         <v>29098.36</v>
       </c>
-      <c r="H86" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I86" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>35500</v>
       </c>
     </row>
     <row r="87">
@@ -3530,13 +3791,16 @@
         <v>0.7</v>
       </c>
       <c r="G87" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H87" s="5" t="n">
         <v>81475.41</v>
       </c>
-      <c r="H87" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I87" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>99400</v>
       </c>
     </row>
     <row r="88">
@@ -3565,13 +3829,16 @@
         <v>0.2</v>
       </c>
       <c r="G88" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H88" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H88" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I88" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="89">
@@ -3600,13 +3867,16 @@
         <v>0.1</v>
       </c>
       <c r="G89" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H89" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H89" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I89" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="90">
@@ -3635,13 +3905,16 @@
         <v>0.05</v>
       </c>
       <c r="G90" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H90" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H90" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I90" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="91">
@@ -3670,13 +3943,16 @@
         <v>0.038</v>
       </c>
       <c r="G91" s="5" t="n">
+        <v>275655.74</v>
+      </c>
+      <c r="H91" s="5" t="n">
         <v>10474.92</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>275655.74</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>336300</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>12779.4</v>
       </c>
     </row>
     <row r="92">
@@ -3705,13 +3981,16 @@
         <v>0.1</v>
       </c>
       <c r="G92" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H92" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="93">
@@ -3740,13 +4019,16 @@
         <v>0.1</v>
       </c>
       <c r="G93" s="5" t="n">
+        <v>145081.97</v>
+      </c>
+      <c r="H93" s="5" t="n">
         <v>14508.2</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>145081.97</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>177000</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>17700</v>
       </c>
     </row>
     <row r="94">
@@ -3775,13 +4057,16 @@
         <v>0.1</v>
       </c>
       <c r="G94" s="5" t="n">
+        <v>145081.97</v>
+      </c>
+      <c r="H94" s="5" t="n">
         <v>14508.2</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>145081.97</v>
       </c>
       <c r="I94" s="5" t="n">
         <v>177000</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>17700</v>
       </c>
     </row>
     <row r="95">
@@ -3810,13 +4095,16 @@
         <v>0.1</v>
       </c>
       <c r="G95" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H95" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I95" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="96">
@@ -3845,13 +4133,16 @@
         <v>0.05</v>
       </c>
       <c r="G96" s="5" t="n">
+        <v>275655.74</v>
+      </c>
+      <c r="H96" s="5" t="n">
         <v>13782.79</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>275655.74</v>
       </c>
       <c r="I96" s="5" t="n">
         <v>336300</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>16815</v>
       </c>
     </row>
     <row r="97">
@@ -3880,13 +4171,16 @@
         <v>0.05</v>
       </c>
       <c r="G97" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H97" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H97" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I97" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="98">
@@ -3915,13 +4209,16 @@
         <v>0.05</v>
       </c>
       <c r="G98" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H98" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H98" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I98" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="99">
@@ -3950,13 +4247,16 @@
         <v>0.2</v>
       </c>
       <c r="G99" s="5" t="n">
+        <v>145081.97</v>
+      </c>
+      <c r="H99" s="5" t="n">
         <v>29016.39</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>145081.97</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>177000</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>35400</v>
       </c>
     </row>
     <row r="100">
@@ -3985,13 +4285,16 @@
         <v>0.05</v>
       </c>
       <c r="G100" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H100" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I100" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="101">
@@ -4020,13 +4323,16 @@
         <v>0.1</v>
       </c>
       <c r="G101" s="5" t="n">
+        <v>145081.97</v>
+      </c>
+      <c r="H101" s="5" t="n">
         <v>14508.2</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>145081.97</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>177000</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>17700</v>
       </c>
     </row>
     <row r="102">
@@ -4055,13 +4361,16 @@
         <v>0.11</v>
       </c>
       <c r="G102" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H102" s="5" t="n">
         <v>14155.74</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>17270</v>
       </c>
     </row>
     <row r="103">
@@ -4090,13 +4399,16 @@
         <v>0.2</v>
       </c>
       <c r="G103" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H103" s="5" t="n">
         <v>25737.7</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>31399.99</v>
       </c>
     </row>
     <row r="104">
@@ -4125,13 +4437,16 @@
         <v>0.2</v>
       </c>
       <c r="G104" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H104" s="5" t="n">
         <v>25737.7</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I104" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>31399.99</v>
       </c>
     </row>
     <row r="105">
@@ -4160,13 +4475,16 @@
         <v>0.1</v>
       </c>
       <c r="G105" s="5" t="n">
+        <v>265000</v>
+      </c>
+      <c r="H105" s="5" t="n">
         <v>26500</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>265000</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>323300</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>32330</v>
       </c>
     </row>
     <row r="106">
@@ -4195,13 +4513,16 @@
         <v>0.15</v>
       </c>
       <c r="G106" s="5" t="n">
+        <v>192622.95</v>
+      </c>
+      <c r="H106" s="5" t="n">
         <v>28893.44</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>192622.95</v>
       </c>
       <c r="I106" s="5" t="n">
         <v>235000</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>35250</v>
       </c>
     </row>
     <row r="107">
@@ -4230,13 +4551,16 @@
         <v>0.005</v>
       </c>
       <c r="G107" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H107" s="5" t="n">
         <v>1017.62</v>
-      </c>
-      <c r="H107" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>1241.5</v>
       </c>
     </row>
     <row r="108">
@@ -4265,13 +4589,16 @@
         <v>0.004</v>
       </c>
       <c r="G108" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H108" s="5" t="n">
         <v>475.41</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="109">
@@ -4300,13 +4627,16 @@
         <v>0.005</v>
       </c>
       <c r="G109" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H109" s="5" t="n">
         <v>1017.62</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>1241.5</v>
       </c>
     </row>
     <row r="110">
@@ -4335,13 +4665,16 @@
         <v>0.004</v>
       </c>
       <c r="G110" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H110" s="5" t="n">
         <v>475.41</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I110" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="111">
@@ -4370,13 +4703,16 @@
         <v>0.005</v>
       </c>
       <c r="G111" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H111" s="5" t="n">
         <v>1017.62</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>1241.5</v>
       </c>
     </row>
     <row r="112">
@@ -4405,13 +4741,16 @@
         <v>0.004</v>
       </c>
       <c r="G112" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H112" s="5" t="n">
         <v>475.41</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I112" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="113">
@@ -4440,13 +4779,16 @@
         <v>0.005</v>
       </c>
       <c r="G113" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H113" s="5" t="n">
         <v>1017.62</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>1241.5</v>
       </c>
     </row>
     <row r="114">
@@ -4475,13 +4817,16 @@
         <v>0.004</v>
       </c>
       <c r="G114" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H114" s="5" t="n">
         <v>475.41</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="115">
@@ -4510,13 +4855,16 @@
         <v>0.17</v>
       </c>
       <c r="G115" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H115" s="5" t="n">
         <v>20204.92</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>24650</v>
       </c>
     </row>
     <row r="116">
@@ -4545,13 +4893,16 @@
         <v>0.02</v>
       </c>
       <c r="G116" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H116" s="5" t="n">
         <v>5491.8</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I116" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>6700</v>
       </c>
     </row>
     <row r="117">
@@ -4580,13 +4931,16 @@
         <v>0.15</v>
       </c>
       <c r="G117" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H117" s="5" t="n">
         <v>17827.87</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>21750</v>
       </c>
     </row>
     <row r="118">
@@ -4615,13 +4969,16 @@
         <v>0.144</v>
       </c>
       <c r="G118" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H118" s="5" t="n">
         <v>17114.75</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I118" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>20879.99</v>
       </c>
     </row>
     <row r="119">
@@ -4650,13 +5007,16 @@
         <v>0.04</v>
       </c>
       <c r="G119" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H119" s="5" t="n">
         <v>4754.1</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>5800</v>
       </c>
     </row>
     <row r="120">
@@ -4685,13 +5045,16 @@
         <v>0.16</v>
       </c>
       <c r="G120" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H120" s="5" t="n">
         <v>19016.39</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I120" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="121">
@@ -4720,13 +5083,16 @@
         <v>0.03</v>
       </c>
       <c r="G121" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H121" s="5" t="n">
         <v>8237.700000000001</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>10049.99</v>
       </c>
     </row>
     <row r="122">
@@ -4755,13 +5121,16 @@
         <v>0.09</v>
       </c>
       <c r="G122" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H122" s="5" t="n">
         <v>10696.72</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I122" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>13050</v>
       </c>
     </row>
     <row r="123">
@@ -4790,13 +5159,16 @@
         <v>0.025</v>
       </c>
       <c r="G123" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H123" s="5" t="n">
         <v>6864.75</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>8374.99</v>
       </c>
     </row>
     <row r="124">
@@ -4825,13 +5197,16 @@
         <v>0.02</v>
       </c>
       <c r="G124" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H124" s="5" t="n">
         <v>2327.87</v>
       </c>
-      <c r="H124" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I124" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>2840</v>
       </c>
     </row>
     <row r="125">
@@ -4860,13 +5235,16 @@
         <v>0.14</v>
       </c>
       <c r="G125" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H125" s="5" t="n">
         <v>16639.34</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I125" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>20299.99</v>
       </c>
     </row>
     <row r="126">
@@ -4895,13 +5273,16 @@
         <v>0.3</v>
       </c>
       <c r="G126" s="5" t="n">
+        <v>120491.8</v>
+      </c>
+      <c r="H126" s="5" t="n">
         <v>36147.54</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>120491.8</v>
       </c>
       <c r="I126" s="5" t="n">
         <v>147000</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>44100</v>
       </c>
     </row>
     <row r="127">
@@ -4930,13 +5311,16 @@
         <v>0.48</v>
       </c>
       <c r="G127" s="5" t="n">
+        <v>143442.62</v>
+      </c>
+      <c r="H127" s="5" t="n">
         <v>68852.46000000001</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>143442.62</v>
       </c>
       <c r="I127" s="5" t="n">
         <v>175000</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>84000</v>
       </c>
     </row>
     <row r="128">
@@ -4965,13 +5349,16 @@
         <v>0.11</v>
       </c>
       <c r="G128" s="5" t="n">
+        <v>274590.16</v>
+      </c>
+      <c r="H128" s="5" t="n">
         <v>30204.92</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>274590.16</v>
       </c>
       <c r="I128" s="5" t="n">
         <v>335000</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>36850</v>
       </c>
     </row>
     <row r="129">
@@ -5000,13 +5387,16 @@
         <v>0.19</v>
       </c>
       <c r="G129" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H129" s="5" t="n">
         <v>22581.97</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I129" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>27550</v>
       </c>
     </row>
     <row r="130">
@@ -5035,13 +5425,16 @@
         <v>0.32</v>
       </c>
       <c r="G130" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H130" s="5" t="n">
         <v>37245.9</v>
       </c>
-      <c r="H130" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I130" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>45440</v>
       </c>
     </row>
     <row r="131">
@@ -5070,13 +5463,16 @@
         <v>0.03</v>
       </c>
       <c r="G131" s="5" t="n">
+        <v>120491.8</v>
+      </c>
+      <c r="H131" s="5" t="n">
         <v>3614.75</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>120491.8</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>147000</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>4409.99</v>
       </c>
     </row>
     <row r="132">
@@ -5105,13 +5501,16 @@
         <v>0.03</v>
       </c>
       <c r="G132" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H132" s="5" t="n">
         <v>6105.74</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I132" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>7449</v>
       </c>
     </row>
     <row r="133">
@@ -5140,13 +5539,16 @@
         <v>0.02</v>
       </c>
       <c r="G133" s="5" t="n">
+        <v>161475.41</v>
+      </c>
+      <c r="H133" s="5" t="n">
         <v>3229.51</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>161475.41</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>197000</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>3940</v>
       </c>
     </row>
     <row r="134">
@@ -5175,13 +5577,16 @@
         <v>0.09</v>
       </c>
       <c r="G134" s="5" t="n">
+        <v>192622.95</v>
+      </c>
+      <c r="H134" s="5" t="n">
         <v>17336.07</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>192622.95</v>
       </c>
       <c r="I134" s="5" t="n">
         <v>235000</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>21150.01</v>
       </c>
     </row>
     <row r="135">
@@ -5210,13 +5615,16 @@
         <v>0.09</v>
       </c>
       <c r="G135" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H135" s="5" t="n">
         <v>10696.72</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I135" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>13050</v>
       </c>
     </row>
     <row r="136">
@@ -5245,13 +5653,16 @@
         <v>0.09</v>
       </c>
       <c r="G136" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H136" s="5" t="n">
         <v>10696.72</v>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I136" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>13050</v>
       </c>
     </row>
     <row r="137">
@@ -5280,13 +5691,16 @@
         <v>0.1</v>
       </c>
       <c r="G137" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H137" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I137" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="138">
@@ -5315,13 +5729,16 @@
         <v>0.7</v>
       </c>
       <c r="G138" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H138" s="5" t="n">
         <v>81475.41</v>
       </c>
-      <c r="H138" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I138" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>99400</v>
       </c>
     </row>
     <row r="139">
@@ -5350,13 +5767,16 @@
         <v>0.05</v>
       </c>
       <c r="G139" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H139" s="5" t="n">
         <v>11639.34</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I139" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="140">
@@ -5385,13 +5805,16 @@
         <v>0.05</v>
       </c>
       <c r="G140" s="5" t="n">
+        <v>251065.57</v>
+      </c>
+      <c r="H140" s="5" t="n">
         <v>12553.28</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>251065.57</v>
       </c>
       <c r="I140" s="5" t="n">
         <v>306300</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>15315</v>
       </c>
     </row>
     <row r="141">
@@ -5420,13 +5843,16 @@
         <v>0.05</v>
       </c>
       <c r="G141" s="5" t="n">
+        <v>219672.13</v>
+      </c>
+      <c r="H141" s="5" t="n">
         <v>10983.61</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>219672.13</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>268000</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>13400</v>
       </c>
     </row>
     <row r="142">
@@ -5455,13 +5881,16 @@
         <v>0.5</v>
       </c>
       <c r="G142" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H142" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H142" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I142" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="143">
@@ -5490,13 +5919,16 @@
         <v>0.3</v>
       </c>
       <c r="G143" s="5" t="n">
+        <v>120491.8</v>
+      </c>
+      <c r="H143" s="5" t="n">
         <v>36147.54</v>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>120491.8</v>
       </c>
       <c r="I143" s="5" t="n">
         <v>147000</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>44100</v>
       </c>
     </row>
     <row r="144">
@@ -5525,13 +5957,16 @@
         <v>0.3</v>
       </c>
       <c r="G144" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H144" s="5" t="n">
         <v>35655.74</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I144" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>43500</v>
       </c>
     </row>
     <row r="145">
@@ -5560,13 +5995,16 @@
         <v>0.5</v>
       </c>
       <c r="G145" s="5" t="n">
+        <v>143442.62</v>
+      </c>
+      <c r="H145" s="5" t="n">
         <v>71721.31</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>143442.62</v>
       </c>
       <c r="I145" s="5" t="n">
         <v>175000</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>87500</v>
       </c>
     </row>
     <row r="146">
@@ -5595,13 +6033,16 @@
         <v>0.1</v>
       </c>
       <c r="G146" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H146" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H146" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I146" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="147">
@@ -5638,6 +6079,9 @@
       <c r="I147" s="5" t="n">
         <v>142000</v>
       </c>
+      <c r="J147" s="5" t="n">
+        <v>142000</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -5665,13 +6109,16 @@
         <v>0.3</v>
       </c>
       <c r="G148" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H148" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H148" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I148" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="149">
@@ -5700,13 +6147,16 @@
         <v>0.38</v>
       </c>
       <c r="G149" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H149" s="5" t="n">
         <v>44229.51</v>
       </c>
-      <c r="H149" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I149" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>53960</v>
       </c>
     </row>
     <row r="150">
@@ -5735,13 +6185,16 @@
         <v>0.25</v>
       </c>
       <c r="G150" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H150" s="5" t="n">
         <v>39344.26</v>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I150" s="5" t="n">
         <v>192000</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>48000</v>
       </c>
     </row>
     <row r="151">
@@ -5770,13 +6223,16 @@
         <v>0.1</v>
       </c>
       <c r="G151" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H151" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="152">
@@ -5805,13 +6261,16 @@
         <v>0.25</v>
       </c>
       <c r="G152" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H152" s="5" t="n">
         <v>29098.36</v>
       </c>
-      <c r="H152" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I152" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J152" s="5" t="n">
+        <v>35500</v>
       </c>
     </row>
     <row r="153">
@@ -5840,13 +6299,16 @@
         <v>0.1</v>
       </c>
       <c r="G153" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H153" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I153" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="154">
@@ -5875,13 +6337,16 @@
         <v>0.2</v>
       </c>
       <c r="G154" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H154" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H154" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I154" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J154" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="155">
@@ -5910,13 +6375,16 @@
         <v>0.06</v>
       </c>
       <c r="G155" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H155" s="5" t="n">
         <v>7131.15</v>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I155" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>8700</v>
       </c>
     </row>
     <row r="156">
@@ -5945,13 +6413,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G156" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H156" s="5" t="n">
         <v>8147.54</v>
       </c>
-      <c r="H156" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I156" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>9940</v>
       </c>
     </row>
     <row r="157">
@@ -5980,13 +6451,16 @@
         <v>0.17</v>
       </c>
       <c r="G157" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H157" s="5" t="n">
         <v>19786.89</v>
       </c>
-      <c r="H157" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I157" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>24140.01</v>
       </c>
     </row>
     <row r="158">
@@ -6015,13 +6489,16 @@
         <v>0.031</v>
       </c>
       <c r="G158" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H158" s="5" t="n">
         <v>3608.2</v>
       </c>
-      <c r="H158" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I158" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>4402</v>
       </c>
     </row>
     <row r="159">
@@ -6050,13 +6527,16 @@
         <v>0.031</v>
       </c>
       <c r="G159" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H159" s="5" t="n">
         <v>3608.2</v>
       </c>
-      <c r="H159" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I159" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>4402</v>
       </c>
     </row>
     <row r="160">
@@ -6085,13 +6565,16 @@
         <v>0.2</v>
       </c>
       <c r="G160" s="5" t="n">
+        <v>293196.72</v>
+      </c>
+      <c r="H160" s="5" t="n">
         <v>58639.34</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>293196.72</v>
       </c>
       <c r="I160" s="5" t="n">
         <v>357700</v>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>71539.99000000001</v>
       </c>
     </row>
     <row r="161">
@@ -6120,13 +6603,16 @@
         <v>0.2</v>
       </c>
       <c r="G161" s="5" t="n">
+        <v>219672.13</v>
+      </c>
+      <c r="H161" s="5" t="n">
         <v>43934.43</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>219672.13</v>
       </c>
       <c r="I161" s="5" t="n">
         <v>268000</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>53600</v>
       </c>
     </row>
     <row r="162">
@@ -6155,13 +6641,16 @@
         <v>0.1</v>
       </c>
       <c r="G162" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H162" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I162" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="163">
@@ -6190,13 +6679,16 @@
         <v>0.1</v>
       </c>
       <c r="G163" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H163" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I163" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="164">
@@ -6225,13 +6717,16 @@
         <v>0.1</v>
       </c>
       <c r="G164" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H164" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I164" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="165">
@@ -6260,13 +6755,16 @@
         <v>0.1</v>
       </c>
       <c r="G165" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H165" s="5" t="n">
         <v>12868.85</v>
-      </c>
-      <c r="H165" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I165" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>15700</v>
       </c>
     </row>
     <row r="166">
@@ -6295,13 +6793,16 @@
         <v>0.1</v>
       </c>
       <c r="G166" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H166" s="5" t="n">
         <v>11885.25</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I166" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>14500</v>
       </c>
     </row>
     <row r="167">
@@ -6330,13 +6831,16 @@
         <v>0.3</v>
       </c>
       <c r="G167" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H167" s="5" t="n">
         <v>35655.74</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I167" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>43500</v>
       </c>
     </row>
     <row r="168">
@@ -6365,13 +6869,16 @@
         <v>0.3</v>
       </c>
       <c r="G168" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H168" s="5" t="n">
         <v>34918.03</v>
       </c>
-      <c r="H168" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I168" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>42600</v>
       </c>
     </row>
     <row r="169">
@@ -6400,13 +6907,16 @@
         <v>0.2</v>
       </c>
       <c r="G169" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H169" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H169" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I169" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="170">
@@ -6435,13 +6945,16 @@
         <v>0.1</v>
       </c>
       <c r="G170" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H170" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H170" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I170" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J170" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="171">
@@ -6470,13 +6983,16 @@
         <v>0.1</v>
       </c>
       <c r="G171" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H171" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H171" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I171" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="172">
@@ -6505,13 +7021,16 @@
         <v>0.1</v>
       </c>
       <c r="G172" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H172" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H172" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I172" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="173">
@@ -6540,13 +7059,16 @@
         <v>0.2</v>
       </c>
       <c r="G173" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H173" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H173" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I173" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="174">
@@ -6575,13 +7097,16 @@
         <v>0.1</v>
       </c>
       <c r="G174" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H174" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H174" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I174" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="175">
@@ -6610,13 +7135,16 @@
         <v>0.1</v>
       </c>
       <c r="G175" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H175" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H175" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I175" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="176">
@@ -6645,13 +7173,16 @@
         <v>0.1</v>
       </c>
       <c r="G176" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H176" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H176" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I176" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="177">
@@ -6680,13 +7211,16 @@
         <v>0.05</v>
       </c>
       <c r="G177" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H177" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H177" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I177" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="178">
@@ -6715,13 +7249,16 @@
         <v>0.1</v>
       </c>
       <c r="G178" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H178" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H178" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I178" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="179">
@@ -6750,13 +7287,16 @@
         <v>0.1</v>
       </c>
       <c r="G179" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H179" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H179" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I179" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="180">
@@ -6785,13 +7325,16 @@
         <v>0.05</v>
       </c>
       <c r="G180" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H180" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H180" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I180" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="181">
@@ -6820,13 +7363,16 @@
         <v>0.1</v>
       </c>
       <c r="G181" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H181" s="5" t="n">
         <v>11639.34</v>
       </c>
-      <c r="H181" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I181" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="182">
@@ -6855,13 +7401,16 @@
         <v>0.05</v>
       </c>
       <c r="G182" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H182" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H182" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I182" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="183">
@@ -6890,13 +7439,16 @@
         <v>0.05</v>
       </c>
       <c r="G183" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H183" s="5" t="n">
         <v>5819.67</v>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I183" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>7100</v>
       </c>
     </row>
     <row r="184">
@@ -6925,13 +7477,16 @@
         <v>0.01</v>
       </c>
       <c r="G184" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H184" s="5" t="n">
         <v>2327.87</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I184" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>2840</v>
       </c>
     </row>
     <row r="185">
@@ -6960,13 +7515,16 @@
         <v>0.05</v>
       </c>
       <c r="G185" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H185" s="5" t="n">
         <v>11639.34</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I185" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J185" s="5" t="n">
+        <v>14199.99</v>
       </c>
     </row>
     <row r="186">
@@ -6995,13 +7553,16 @@
         <v>0.03</v>
       </c>
       <c r="G186" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H186" s="5" t="n">
         <v>6983.61</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I186" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J186" s="5" t="n">
+        <v>8520</v>
       </c>
     </row>
     <row r="187">
@@ -7030,13 +7591,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G187" s="5" t="n">
+        <v>70491.8</v>
+      </c>
+      <c r="H187" s="5" t="n">
         <v>4934.43</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>70491.8</v>
       </c>
       <c r="I187" s="5" t="n">
         <v>86000</v>
+      </c>
+      <c r="J187" s="5" t="n">
+        <v>6020</v>
       </c>
     </row>
     <row r="188">
@@ -7065,13 +7629,16 @@
         <v>0.2</v>
       </c>
       <c r="G188" s="5" t="n">
+        <v>206557.38</v>
+      </c>
+      <c r="H188" s="5" t="n">
         <v>41311.48</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>206557.38</v>
       </c>
       <c r="I188" s="5" t="n">
         <v>252000</v>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>50400.01</v>
       </c>
     </row>
     <row r="189">
@@ -7100,13 +7667,16 @@
         <v>0.2</v>
       </c>
       <c r="G189" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H189" s="5" t="n">
         <v>46557.38</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I189" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="190">
@@ -7135,13 +7705,16 @@
         <v>0.4</v>
       </c>
       <c r="G190" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H190" s="5" t="n">
         <v>47540.98</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I190" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J190" s="5" t="n">
+        <v>58000</v>
       </c>
     </row>
     <row r="191">
@@ -7170,13 +7743,16 @@
         <v>0.2</v>
       </c>
       <c r="G191" s="5" t="n">
+        <v>192622.95</v>
+      </c>
+      <c r="H191" s="5" t="n">
         <v>38524.59</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>192622.95</v>
       </c>
       <c r="I191" s="5" t="n">
         <v>235000</v>
+      </c>
+      <c r="J191" s="5" t="n">
+        <v>47000</v>
       </c>
     </row>
     <row r="192">
@@ -7205,13 +7781,16 @@
         <v>0.2</v>
       </c>
       <c r="G192" s="5" t="n">
+        <v>206557.38</v>
+      </c>
+      <c r="H192" s="5" t="n">
         <v>41311.48</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>206557.38</v>
       </c>
       <c r="I192" s="5" t="n">
         <v>252000</v>
+      </c>
+      <c r="J192" s="5" t="n">
+        <v>50400.01</v>
       </c>
     </row>
     <row r="193">
@@ -7240,13 +7819,16 @@
         <v>0.2</v>
       </c>
       <c r="G193" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H193" s="5" t="n">
         <v>46557.38</v>
-      </c>
-      <c r="H193" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I193" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="194">
@@ -7275,13 +7857,16 @@
         <v>0.5</v>
       </c>
       <c r="G194" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H194" s="5" t="n">
         <v>59426.23</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I194" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>72500</v>
       </c>
     </row>
     <row r="195">
@@ -7310,13 +7895,16 @@
         <v>0.2</v>
       </c>
       <c r="G195" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H195" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I195" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J195" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="196">
@@ -7345,13 +7933,16 @@
         <v>0.2</v>
       </c>
       <c r="G196" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H196" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H196" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I196" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J196" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="197">
@@ -7380,13 +7971,16 @@
         <v>0.2</v>
       </c>
       <c r="G197" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H197" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H197" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I197" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J197" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="198">
@@ -7415,13 +8009,16 @@
         <v>0.2</v>
       </c>
       <c r="G198" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H198" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H198" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I198" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="199">
@@ -7450,13 +8047,16 @@
         <v>0.2</v>
       </c>
       <c r="G199" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H199" s="5" t="n">
         <v>23278.69</v>
       </c>
-      <c r="H199" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I199" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>28400</v>
       </c>
     </row>
     <row r="200">
@@ -7485,13 +8085,16 @@
         <v>0.081</v>
       </c>
       <c r="G200" s="5" t="n">
+        <v>232786.89</v>
+      </c>
+      <c r="H200" s="5" t="n">
         <v>18855.74</v>
-      </c>
-      <c r="H200" s="5" t="n">
-        <v>232786.89</v>
       </c>
       <c r="I200" s="5" t="n">
         <v>284000</v>
+      </c>
+      <c r="J200" s="5" t="n">
+        <v>23004</v>
       </c>
     </row>
     <row r="201">
@@ -7520,13 +8123,16 @@
         <v>0.22</v>
       </c>
       <c r="G201" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H201" s="5" t="n">
         <v>25606.56</v>
       </c>
-      <c r="H201" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I201" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>31240</v>
       </c>
     </row>
     <row r="202">
@@ -7555,13 +8161,16 @@
         <v>0.26</v>
       </c>
       <c r="G202" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H202" s="5" t="n">
         <v>30262.3</v>
       </c>
-      <c r="H202" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I202" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>36920.01</v>
       </c>
     </row>
     <row r="203">
@@ -7590,13 +8199,16 @@
         <v>0.05</v>
       </c>
       <c r="G203" s="5" t="n">
+        <v>203524.59</v>
+      </c>
+      <c r="H203" s="5" t="n">
         <v>10176.23</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>203524.59</v>
       </c>
       <c r="I203" s="5" t="n">
         <v>248300</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>12415</v>
       </c>
     </row>
     <row r="204">
@@ -7625,13 +8237,16 @@
         <v>0.4</v>
       </c>
       <c r="G204" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H204" s="5" t="n">
         <v>46557.38</v>
       </c>
-      <c r="H204" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I204" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J204" s="5" t="n">
+        <v>56800</v>
       </c>
     </row>
     <row r="205">
@@ -7660,13 +8275,16 @@
         <v>0.3</v>
       </c>
       <c r="G205" s="5" t="n">
+        <v>118852.46</v>
+      </c>
+      <c r="H205" s="5" t="n">
         <v>35655.74</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>118852.46</v>
       </c>
       <c r="I205" s="5" t="n">
         <v>145000</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>43500</v>
       </c>
     </row>
     <row r="206">
@@ -7695,13 +8313,16 @@
         <v>0.5</v>
       </c>
       <c r="G206" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H206" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H206" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I206" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J206" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="207">
@@ -7730,13 +8351,16 @@
         <v>0.36</v>
       </c>
       <c r="G207" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H207" s="5" t="n">
         <v>41901.64</v>
       </c>
-      <c r="H207" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I207" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>51120</v>
       </c>
     </row>
     <row r="208">
@@ -7765,13 +8389,16 @@
         <v>0.36</v>
       </c>
       <c r="G208" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H208" s="5" t="n">
         <v>41901.64</v>
       </c>
-      <c r="H208" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I208" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J208" s="5" t="n">
+        <v>51120</v>
       </c>
     </row>
     <row r="209">
@@ -7800,13 +8427,16 @@
         <v>0.36</v>
       </c>
       <c r="G209" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H209" s="5" t="n">
         <v>41901.64</v>
       </c>
-      <c r="H209" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I209" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>51120</v>
       </c>
     </row>
     <row r="210">
@@ -7835,13 +8465,16 @@
         <v>0.5</v>
       </c>
       <c r="G210" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H210" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H210" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I210" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="211">
@@ -7870,13 +8503,16 @@
         <v>0.5</v>
       </c>
       <c r="G211" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H211" s="5" t="n">
         <v>58196.72</v>
       </c>
-      <c r="H211" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I211" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J211" s="5" t="n">
+        <v>71000</v>
       </c>
     </row>
     <row r="212">
@@ -7905,13 +8541,16 @@
         <v>0.1</v>
       </c>
       <c r="G212" s="5" t="n">
+        <v>363442.62</v>
+      </c>
+      <c r="H212" s="5" t="n">
         <v>36344.26</v>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>363442.62</v>
       </c>
       <c r="I212" s="5" t="n">
         <v>443400</v>
+      </c>
+      <c r="J212" s="5" t="n">
+        <v>44340</v>
       </c>
     </row>
     <row r="213">
@@ -7940,13 +8579,16 @@
         <v>0.1</v>
       </c>
       <c r="G213" s="5" t="n">
+        <v>265000</v>
+      </c>
+      <c r="H213" s="5" t="n">
         <v>26500</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>265000</v>
       </c>
       <c r="I213" s="5" t="n">
         <v>323300</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>32330</v>
       </c>
     </row>
     <row r="214">
@@ -7983,6 +8625,9 @@
       <c r="I214" s="5" t="n">
         <v>175000</v>
       </c>
+      <c r="J214" s="5" t="n">
+        <v>175000</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -8010,13 +8655,16 @@
         <v>0.03</v>
       </c>
       <c r="G215" s="5" t="n">
+        <v>210655.74</v>
+      </c>
+      <c r="H215" s="5" t="n">
         <v>6319.67</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>210655.74</v>
       </c>
       <c r="I215" s="5" t="n">
         <v>257000</v>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>7710</v>
       </c>
     </row>
     <row r="216">
@@ -8053,6 +8701,9 @@
       <c r="I216" s="5" t="n">
         <v>147000</v>
       </c>
+      <c r="J216" s="5" t="n">
+        <v>147000</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -8088,6 +8739,9 @@
       <c r="I217" s="5" t="n">
         <v>284000</v>
       </c>
+      <c r="J217" s="5" t="n">
+        <v>284000.01</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -8115,13 +8769,16 @@
         <v>0.277</v>
       </c>
       <c r="G218" s="5" t="n">
+        <v>149180.33</v>
+      </c>
+      <c r="H218" s="5" t="n">
         <v>41322.95</v>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>149180.33</v>
       </c>
       <c r="I218" s="5" t="n">
         <v>182000</v>
+      </c>
+      <c r="J218" s="5" t="n">
+        <v>50414</v>
       </c>
     </row>
     <row r="219">
@@ -8150,13 +8807,16 @@
         <v>0.35</v>
       </c>
       <c r="G219" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H219" s="5" t="n">
         <v>40737.7</v>
       </c>
-      <c r="H219" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I219" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J219" s="5" t="n">
+        <v>49699.99</v>
       </c>
     </row>
     <row r="220">
@@ -8185,13 +8845,16 @@
         <v>0.3</v>
       </c>
       <c r="G220" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H220" s="5" t="n">
         <v>38606.56</v>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I220" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>47100</v>
       </c>
     </row>
     <row r="221">
@@ -8220,13 +8883,16 @@
         <v>0.15</v>
       </c>
       <c r="G221" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H221" s="5" t="n">
         <v>17459.02</v>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I221" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>21300</v>
       </c>
     </row>
     <row r="222">
@@ -8255,13 +8921,16 @@
         <v>2</v>
       </c>
       <c r="G222" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H222" s="5" t="n">
         <v>232786.89</v>
       </c>
-      <c r="H222" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I222" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J222" s="5" t="n">
+        <v>284000.01</v>
       </c>
     </row>
     <row r="223">
@@ -8290,13 +8959,16 @@
         <v>0.35</v>
       </c>
       <c r="G223" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H223" s="5" t="n">
         <v>40737.7</v>
       </c>
-      <c r="H223" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I223" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J223" s="5" t="n">
+        <v>49699.99</v>
       </c>
     </row>
     <row r="224">
@@ -8325,13 +8997,16 @@
         <v>0.3</v>
       </c>
       <c r="G224" s="5" t="n">
+        <v>128688.52</v>
+      </c>
+      <c r="H224" s="5" t="n">
         <v>38606.56</v>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>128688.52</v>
       </c>
       <c r="I224" s="5" t="n">
         <v>157000</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>47100</v>
       </c>
     </row>
     <row r="225">
@@ -8360,13 +9035,16 @@
         <v>0.15</v>
       </c>
       <c r="G225" s="5" t="n">
+        <v>116393.44</v>
+      </c>
+      <c r="H225" s="5" t="n">
         <v>17459.02</v>
       </c>
-      <c r="H225" s="5" t="n">
-        <v>116393.44</v>
-      </c>
       <c r="I225" s="5" t="n">
         <v>142000</v>
+      </c>
+      <c r="J225" s="5" t="n">
+        <v>21300</v>
       </c>
     </row>
     <row r="226">
@@ -8395,13 +9073,16 @@
         <v>0.1</v>
       </c>
       <c r="G226" s="5" t="n">
+        <v>200819.67</v>
+      </c>
+      <c r="H226" s="5" t="n">
         <v>20081.97</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>200819.67</v>
       </c>
       <c r="I226" s="5" t="n">
         <v>245000</v>
+      </c>
+      <c r="J226" s="5" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="227">
@@ -8430,14 +9111,17 @@
         <v>1.936</v>
       </c>
       <c r="G227" s="5" t="n">
+        <v>157377.05</v>
+      </c>
+      <c r="H227" s="5" t="n">
         <v>304681.97</v>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>157377.05</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>192000</v>
       </c>
+      <c r="J227" s="5" t="n">
+        <v>371712</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
@@ -8449,7 +9133,16 @@
         <v>72.498</v>
       </c>
       <c r="G228" s="9" t="n">
+        <v>131720.37</v>
+      </c>
+      <c r="H228" s="9" t="n">
         <v>9549463.4</v>
+      </c>
+      <c r="I228" s="9" t="n">
+        <v>160698.85</v>
+      </c>
+      <c r="J228" s="9" t="n">
+        <v>11650345.35</v>
       </c>
     </row>
     <row r="229">
@@ -8458,7 +9151,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G229" s="9" t="n">
+      <c r="H229" s="9" t="n">
         <v>9549463.44262295</v>
       </c>
     </row>
@@ -8468,7 +9161,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F230" s="9" t="n">
+      <c r="J230" s="9" t="n">
         <v>11650345.4</v>
       </c>
     </row>
